--- a/Resources/Data/LightPositionData.xlsx
+++ b/Resources/Data/LightPositionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E372A650-98A9-43F3-98A0-C4D75BC907C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBB80D4-A0E2-4A36-9279-0F465D4011CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="1392" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5664" yWindow="1668" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -488,7 +488,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
         <v>-20</v>
@@ -514,7 +514,7 @@
         <v>-10</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
         <v>-10</v>
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="C4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
         <v>8</v>
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
@@ -592,10 +592,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -615,10 +615,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>10</v>
+        <v>-40</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
@@ -641,13 +641,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>

--- a/Resources/Data/LightPositionData.xlsx
+++ b/Resources/Data/LightPositionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBB80D4-A0E2-4A36-9279-0F465D4011CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398A6CFF-2746-441C-9C82-D0EF34C769A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5664" yWindow="1668" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="192" yWindow="1548" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -485,10 +485,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1">
         <v>-20</v>
@@ -514,7 +514,7 @@
         <v>-10</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
         <v>-10</v>
@@ -540,7 +540,7 @@
         <v>-30</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>8</v>
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
@@ -589,10 +589,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>40</v>
@@ -618,10 +618,10 @@
         <v>-40</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
